--- a/output/admin-reporting/payments-USD.xlsx
+++ b/output/admin-reporting/payments-USD.xlsx
@@ -1942,7 +1942,7 @@
       </c>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -3692,7 +3692,7 @@
       </c>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -3762,7 +3762,7 @@
       </c>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>2026-10-15.1</t>
+          <t>2026-10-24.1</t>
         </is>
       </c>
     </row>
